--- a/sources/julia_step5.xlsx
+++ b/sources/julia_step5.xlsx
@@ -417,27 +417,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:S105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="124" customWidth="1" min="14" max="14"/>
-    <col width="38" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="124" customWidth="1" min="15" max="15"/>
     <col width="38" customWidth="1" min="16" max="16"/>
     <col width="38" customWidth="1" min="17" max="17"/>
-    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="38" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,12 +466,12 @@
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
@@ -495,45 +496,50 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -560,22 +566,27 @@
           <t>35</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>ab6d9b06-f5f7-4feb-9f49-383448e4e096</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>82e2360f-3cd0-425d-af5a-c5d8e5e52627</t>
         </is>
@@ -602,22 +613,27 @@
           <t>30</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>ed821a05-2ec4-494a-a83b-a9d19455605a</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>d29502bb-765d-44e2-8876-21234ac961c4</t>
         </is>
@@ -644,22 +660,27 @@
           <t>37</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0ecb3935-db08-456b-9028-a384f068cad7</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>bd4883ff-ba97-43f1-8b7a-e75e4b235bd4</t>
         </is>
@@ -686,22 +707,27 @@
           <t>30</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>8c936c68-0894-4e5c-a2be-40ff8f18293a</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>6fcd28c4-ed8d-4248-a970-04c30fdf4c0c</t>
         </is>
@@ -710,7 +736,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>FC,db,d,db+1+2</t>
+          <t>FC+db,d,db+1+2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -728,22 +754,27 @@
           <t>45</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>e6a34a80-1f3d-4591-abd0-e675e4465a13</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1beb1ed8-ad26-4266-b8e8-0b6b1905d4fd</t>
         </is>
@@ -770,22 +801,27 @@
           <t>14,14,14</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>e276813a-1ee1-4285-afb3-2cc48b9ea3f7</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>abc48219-3324-45bc-b4e5-eba12deb6d7b</t>
         </is>
@@ -807,27 +843,32 @@
           <t>12</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Special Tag Throw with Michelle only. Michelle finishes with a Lariat. Total damage is 12,24.</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -854,22 +895,27 @@
           <t>40</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -896,22 +942,27 @@
           <t>45</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -938,22 +989,27 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>b70b8f8a-633b-40a2-8811-5f4191813631</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -985,12 +1041,12 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
@@ -1015,45 +1071,50 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K15" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K15" s="1" t="inlineStr">
+      <c r="L15" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L15" s="1" t="inlineStr">
+      <c r="M15" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M15" s="1" t="inlineStr">
+      <c r="N15" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N15" s="1" t="inlineStr">
+      <c r="O15" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O15" s="1" t="inlineStr">
+      <c r="P15" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P15" s="1" t="inlineStr">
+      <c r="Q15" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q15" s="1" t="inlineStr">
+      <c r="R15" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R15" s="1" t="inlineStr">
+      <c r="S15" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1092,15 +1153,20 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>15035c38-d5a6-49f9-bea8-f587a7392e1a</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>624135a9-7295-48fa-ba6c-31a86bc446c3</t>
         </is>
@@ -1139,15 +1205,20 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>8e21dae9-4968-476e-b16c-22b5b747ee5e</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>4e8f95f2-3777-4134-9089-cbf3b2fe7533</t>
         </is>
@@ -1186,15 +1257,20 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>6e6b42cc-fe86-458b-9922-127dc30031c0</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>2ee732ff-25d9-46a8-8c45-e56593085910</t>
         </is>
@@ -1233,15 +1309,20 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>cca5e538-aae6-400e-a730-3420008d1646</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>6f72c047-a692-4df5-a606-8eafb518215d</t>
         </is>
@@ -1250,7 +1331,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F,1</t>
+          <t>f+1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1280,15 +1361,20 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>a6a7b0f8-e04c-46c8-bd17-e2f073028d01</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>45938629-f4a5-4400-9d57-551381ccaddd</t>
         </is>
@@ -1297,7 +1383,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F,2</t>
+          <t>f+2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1327,15 +1413,20 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>1af6facc-f33e-491c-8dce-850506bd0cf8</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>7a6f27d8-bf4f-4e57-8fc6-2c7353a60dba</t>
         </is>
@@ -1344,7 +1435,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F,3</t>
+          <t>f+3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1374,15 +1465,20 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>78a06659-d397-4743-bd01-9a9482d267b3</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>05488562-ac28-47a2-9d89-19c17aab4ef3</t>
         </is>
@@ -1391,7 +1487,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F,4</t>
+          <t>f+4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1421,15 +1517,20 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>e4927ca5-bc4d-460d-adae-c61141dbfdcb</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>8795513e-8417-4e86-b8ba-a6a98274ff37</t>
         </is>
@@ -1468,15 +1569,20 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>e22b57f5-5424-4c98-a000-6bb30da58f45</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>f4bd9baf-693c-4965-9b51-209ffe480dec</t>
         </is>
@@ -1515,15 +1621,20 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>646872c0-d619-4bbc-b72f-00e9b79ef036</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>c380c889-63ec-46ed-b1e8-16139acf8b7d</t>
         </is>
@@ -1562,15 +1673,20 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>2897ab35-7c69-4caf-8eaa-9ff9f8372fe1</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>7db50050-6a19-4e76-85b6-2b01cc4350eb</t>
         </is>
@@ -1609,15 +1725,20 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>4b126cb7-06af-4478-856c-bc3c55d1e6e1</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>9559c6a0-e111-4c90-98a8-17922e344950</t>
         </is>
@@ -1626,7 +1747,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FC 1</t>
+          <t>FC+1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1656,15 +1777,20 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>0dacef04-e59d-419d-81f2-aeb369ac7ff0</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>52254c0f-0579-4e8b-bb82-9bf23b82c059</t>
         </is>
@@ -1673,7 +1799,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FC 2</t>
+          <t>FC+2</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1703,15 +1829,20 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>s</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>722d6e66-1274-44d2-ad76-2c4724acf79c</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>5d9e08dc-586c-42e0-b05d-d53e0722c953</t>
         </is>
@@ -1720,7 +1851,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FC 3</t>
+          <t>FC+3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1750,15 +1881,20 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>0b5550a4-0c1a-4674-ba2e-3a1456aa5577</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>13c153c4-7ad5-483e-8a55-9ca62e530507</t>
         </is>
@@ -1767,7 +1903,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FC 4</t>
+          <t>FC+4</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1797,15 +1933,20 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>l</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>f486bcc7-f067-4a17-b512-ff2d8292f640</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>bf0d7423-b624-466a-847b-1c1c6c3e527d</t>
         </is>
@@ -1814,7 +1955,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>WS 1</t>
+          <t>WS+1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1844,15 +1985,20 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>515dca44-c4b4-4aac-8a57-a5bd63dca6a7</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>78a7a936-3e93-40d8-8cee-62959e8cf78a</t>
         </is>
@@ -1861,7 +2007,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WS 2</t>
+          <t>WS+2</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1891,15 +2037,20 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>0e2c078f-d1de-4d37-9205-f427cbbe022f</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>54235914-59eb-4a20-b36d-91c541cc2e94</t>
         </is>
@@ -1908,7 +2059,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>WS 3</t>
+          <t>WS+3</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -1938,15 +2089,20 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>4d3a0917-e813-4c55-9da5-3e9775c5241a</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>778d503d-7812-4de4-b0ef-96a4b78ba20c</t>
         </is>
@@ -1955,7 +2111,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WS 4</t>
+          <t>WS+4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1985,15 +2141,20 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>fcb15e85-d11e-41bb-b153-1f50e75b8ba0</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>2729435e-e9ba-439c-b813-74909c92bb10</t>
         </is>
@@ -2032,15 +2193,20 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>81941edd-8313-4c5d-808a-69e5391f1646</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>2ab0708d-e9f2-4cfe-9bfe-4182938cf9c5</t>
         </is>
@@ -2079,15 +2245,20 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>5de20d7c-6e9f-4b4d-b3be-6f3019ed23d4</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>a8b16b5c-ff44-4b9e-943a-590946b12392</t>
         </is>
@@ -2126,15 +2297,20 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>8de3341e-a280-448e-be3c-8871c83bdc2a</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>84a1032e-e3f1-493f-91f8-0a7635613eca</t>
         </is>
@@ -2173,15 +2349,20 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>565e0ea5-fec4-40e7-b756-fceb99f74fe3</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>53380c85-00db-4d12-b976-2b7a7ae68c2a</t>
         </is>
@@ -2213,12 +2394,12 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
@@ -2243,45 +2424,50 @@
       </c>
       <c r="J42" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K42" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K42" s="1" t="inlineStr">
+      <c r="L42" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L42" s="1" t="inlineStr">
+      <c r="M42" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M42" s="1" t="inlineStr">
+      <c r="N42" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N42" s="1" t="inlineStr">
+      <c r="O42" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O42" s="1" t="inlineStr">
+      <c r="P42" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P42" s="1" t="inlineStr">
+      <c r="Q42" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q42" s="1" t="inlineStr">
+      <c r="R42" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R42" s="1" t="inlineStr">
+      <c r="S42" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -2325,20 +2511,25 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>4d1a49f3-ed23-4e20-b00e-1ec062066e8e</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>7dc4a2ca-d636-412a-984b-af70d0bc70b4</t>
         </is>
@@ -2382,20 +2573,25 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>e1224874-813b-4cb5-8863-09a0aa463239</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>20ae85e2-a635-4efe-aa12-c4d7da2120df</t>
         </is>
@@ -2409,7 +2605,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>WR 1</t>
+          <t>WR+1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2444,15 +2640,20 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>2f02cadd-691c-4878-8cc0-ed165628df8d</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>25ce8b7e-9f3a-435f-92d1-f350d26aecc0</t>
         </is>
@@ -2491,25 +2692,30 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>90835ff4-9095-4137-8242-a717dbeaeab8</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>bbd933e6-0ed1-45ae-83ba-d1b80a2aca2b</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>2f02cadd-691c-4878-8cc0-ed165628df8d</t>
         </is>
@@ -2553,15 +2759,20 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>f133d0b0-0e08-4804-a099-7e4bd0e986b5</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>f5055146-693c-4610-927e-1c1ecc7ffd50</t>
         </is>
@@ -2600,25 +2811,30 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>6fff6863-e889-458b-aa91-4b5cc27f07cb</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>8db566fb-78d9-4496-b899-aaa34dbac5dc</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>f133d0b0-0e08-4804-a099-7e4bd0e986b5</t>
         </is>
@@ -2657,20 +2873,25 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>697b57ac-f4e1-4b88-af3c-1c93b7f5ef92</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>cafc3c93-4416-4260-b77c-c2bcb2b34bd1</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>f133d0b0-0e08-4804-a099-7e4bd0e986b5</t>
         </is>
@@ -2714,15 +2935,20 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>cdda1d7c-4cfd-4571-93ca-ca2fd57ed026</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>20d68298-0458-4971-ad79-3bdb2c6bc45d</t>
         </is>
@@ -2761,25 +2987,30 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>efdd89f1-e74a-4052-a24f-85b56505262f</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>3fc32248-c49c-4918-a460-249b714182e7</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>cdda1d7c-4cfd-4571-93ca-ca2fd57ed026</t>
         </is>
@@ -2818,20 +3049,25 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>15cd3b1a-c236-4443-abd8-0bb0c83297ea</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>2e64b986-2f72-4b15-a081-83a778c18d06</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>cdda1d7c-4cfd-4571-93ca-ca2fd57ed026</t>
         </is>
@@ -2875,20 +3111,25 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>hm</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>If the 1st hit is a counter hit, the damage of the 2nd hit will be 10. If the string is complete (1~2~1) the damage is 15.</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>2b4933ca-1985-4996-9512-57f643232731</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>5b055c92-7199-46d7-9a66-b81f058cf33f</t>
         </is>
@@ -2912,30 +3153,35 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>The 3rd only occurs if the 1st hit was a counter hit or the 2nd hit connected on the opponents side.</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>6275a354-d231-4442-8af8-0fc378c274f5</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>df19be7c-d1b5-4569-ad72-d09202c8ce24</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>2b4933ca-1985-4996-9512-57f643232731</t>
         </is>
@@ -2974,25 +3220,30 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>bf4d512c-5f0b-46cc-b1ce-d720fde5db97</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>f86a95d0-6e88-4df9-b0d9-eac609a7dcd1</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>2b4933ca-1985-4996-9512-57f643232731</t>
         </is>
@@ -3031,20 +3282,25 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>23597e7c-315f-44cb-bc68-f45b05b788b8</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>84d6f14f-4c06-4a11-833c-89e4d77303cc</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>2b4933ca-1985-4996-9512-57f643232731</t>
         </is>
@@ -3088,15 +3344,20 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>2fcdf90d-a1c6-4635-b48c-efa347b4bf34</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>eed8a7cc-f9f5-4db5-9a8e-13154acd5f2e</t>
         </is>
@@ -3135,25 +3396,30 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>a0d438e2-6a92-4d84-95e7-ae9c82e1971a</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>06fcb74c-7ef1-4910-baa5-5ff549d169f1</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>2fcdf90d-a1c6-4635-b48c-efa347b4bf34</t>
         </is>
@@ -3197,20 +3463,25 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>a4c9455c-b3f7-445f-bb03-bc9714978245</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>6ea6a131-4528-47b9-b547-5ca7fbc36c49</t>
         </is>
@@ -3254,25 +3525,30 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>JGc</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>The uppercut does not need to be a counter hit to buffer a tag..</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>1242cb0e-50bb-40b6-b2a1-ca87df3c4f00</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>f8303771-3790-4f2d-b82e-a3dd4030c9ac</t>
         </is>
@@ -3316,15 +3592,20 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>ecf9ec9c-b22c-4f6a-9f5c-8f0b3d51b517</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>32c39285-0d95-467e-b604-b48881824316</t>
         </is>
@@ -3368,15 +3649,20 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>0352fade-12a8-40f1-8a4c-f0193680f01a</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>3a9d5340-469a-44ee-bdf1-f63ac00ab3e1</t>
         </is>
@@ -3400,30 +3686,35 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>In the d/f+2,1 string the damage of the d/f+2 is 15. And has to hit from the front to work.</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>c672c34b-05e9-4636-968c-72c907a897d8</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>6d1dada0-2ef7-4f8e-a7b1-3573f3ef791b</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>0352fade-12a8-40f1-8a4c-f0193680f01a</t>
         </is>
@@ -3462,25 +3753,30 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>bbe27077-b04b-4ce7-8f7b-350b6a915118</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>5217e99c-00b5-4542-9d8e-06462325f261</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>0352fade-12a8-40f1-8a4c-f0193680f01a</t>
         </is>
@@ -3519,20 +3815,25 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>71e7fef9-4e10-447a-b667-59a4aa8fc853</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>873ceac2-385c-469e-87f0-b0e08e69ba50</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>0352fade-12a8-40f1-8a4c-f0193680f01a</t>
         </is>
@@ -3581,20 +3882,25 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
           <t>smm</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>93a991d8-f45d-458b-ae7c-eef2802ad600</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>6718fa05-f529-4234-83f2-ea0ff0e53f80</t>
         </is>
@@ -3603,12 +3909,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>WR 2</t>
+          <t>WR+2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FC,df+2</t>
+          <t>FC+df+2</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3643,20 +3949,25 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>FSc</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>68426f4f-f3e0-4291-97a7-3a7bd296591b</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>0576cf8f-0403-4eb2-9a84-e6f6aac6ce18</t>
         </is>
@@ -3665,7 +3976,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SS 2</t>
+          <t>SS+2</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3700,20 +4011,25 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>33acabf7-da8d-4bc4-abdf-3b266034d3f3</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>e29b369c-42e6-465f-a9d8-c71332c19eb2</t>
         </is>
@@ -3762,25 +4078,30 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>The Arm Whip needs to hit for Julia to spin around the opponent.</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>a72aa904-1124-409f-a75b-cb6b7a95fa1f</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>3eaddb93-856e-4286-9afe-2a136672f1c6</t>
         </is>
@@ -3822,22 +4143,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
         <is>
           <t>Causes Special Tag Throw with Michelle, see the Grappling Arts.</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>a2a00b1a-1750-4988-9b6c-606239b6a0c6</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>d7a8e56a-8655-4e7e-8cb3-47b5d679baf6</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>a72aa904-1124-409f-a75b-cb6b7a95fa1f</t>
         </is>
@@ -3846,7 +4172,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WS 2</t>
+          <t>WS+2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3886,20 +4212,25 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>Damage is 18 on the WS+2 if followed by a string starting with 1.</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
+      <c r="P71" t="inlineStr">
         <is>
           <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>95b94296-4b8a-4a81-a3d9-ac54f7eb3fb5</t>
         </is>
@@ -3938,20 +4269,25 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
+      <c r="P72" t="inlineStr">
         <is>
           <t>b8c08be0-1649-4e4f-928e-d221c2f8bf81</t>
         </is>
       </c>
-      <c r="P72" t="inlineStr">
+      <c r="Q72" t="inlineStr">
         <is>
           <t>97fbf846-d9a5-4bd3-adb7-98dc363d6569</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="R72" t="inlineStr">
         <is>
           <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
@@ -3990,30 +4326,35 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>The uppercut does not juggle, but you can buffer in a tag.</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
+      <c r="P73" t="inlineStr">
         <is>
           <t>16ae29bf-13c7-48a7-944e-bb7331713538</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>66ffb7fc-f605-44d7-b667-64994515726d</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="R73" t="inlineStr">
         <is>
           <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
@@ -4052,20 +4393,25 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>mLm</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
+      <c r="P74" t="inlineStr">
         <is>
           <t>3308856d-d15f-45c7-8281-db3de8f037ce</t>
         </is>
       </c>
-      <c r="P74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>33e320b0-7e12-4ae7-9cc4-7c606aaca590</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="R74" t="inlineStr">
         <is>
           <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
@@ -4104,25 +4450,30 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>6379a4b4-d174-412f-8409-cb6229426a50</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>50b918b4-648d-4f4f-b682-2319b146469a</t>
         </is>
@@ -4161,20 +4512,25 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O76" t="inlineStr">
+      <c r="P76" t="inlineStr">
         <is>
           <t>90abd81b-c322-4086-ac5e-1bb4b74d0f21</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>96906e1d-ecb7-4784-8c38-de478dfb34ac</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
         </is>
@@ -4213,25 +4569,30 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>8780c530-485c-4854-86c9-3d8d73cf1f42</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>feea5066-7c67-4d48-8e48-c23ce014a41a</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
         </is>
@@ -4270,25 +4631,30 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O78" t="inlineStr">
+      <c r="P78" t="inlineStr">
         <is>
           <t>d636b20f-0a5f-4b70-aea5-7122dee324e0</t>
         </is>
       </c>
-      <c r="P78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>4d530135-e440-4d11-8033-58319f9a4200</t>
         </is>
       </c>
-      <c r="Q78" t="inlineStr">
+      <c r="R78" t="inlineStr">
         <is>
           <t>08cc0684-9307-4b9b-aa17-ec26f1a07ab2</t>
         </is>
@@ -4332,20 +4698,25 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>MS PLDc</t>
         </is>
       </c>
-      <c r="O79" t="inlineStr">
+      <c r="P79" t="inlineStr">
         <is>
           <t>081c71d9-14c8-4f81-a116-e770a0b1a68b</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>49aebb0f-7e34-49a0-a13f-9792bb666e6f</t>
         </is>
@@ -4389,15 +4760,20 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
           <t>M</t>
         </is>
       </c>
-      <c r="O80" t="inlineStr">
+      <c r="P80" t="inlineStr">
         <is>
           <t>841212ca-51a4-49fb-aa7a-fd658c5efc8f</t>
         </is>
       </c>
-      <c r="P80" t="inlineStr">
+      <c r="Q80" t="inlineStr">
         <is>
           <t>04773d5e-051d-4d43-bcc6-1676ca9c396e</t>
         </is>
@@ -4424,17 +4800,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr">
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
         <is>
           <t>Chains into Spinning Razor Kick Variations. First kick will do 20 damage.</t>
         </is>
       </c>
-      <c r="O81" t="inlineStr">
+      <c r="P81" t="inlineStr">
         <is>
           <t>ad154462-6148-4f1a-8a02-ea05b3eeb7b2</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
+      <c r="Q81" t="inlineStr">
         <is>
           <t>778fe738-736a-40c6-bcdb-37d9cc30283f</t>
         </is>
@@ -4478,20 +4859,25 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O82" t="inlineStr">
+      <c r="P82" t="inlineStr">
         <is>
           <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
         </is>
       </c>
-      <c r="P82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>3f71e6df-2a62-4e24-83a5-cb74227d6235</t>
         </is>
@@ -4530,20 +4916,25 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O83" t="inlineStr">
+      <c r="P83" t="inlineStr">
         <is>
           <t>f3d36877-1a28-4c01-bab8-8229b80b79da</t>
         </is>
       </c>
-      <c r="P83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>bf72a458-da43-4a73-ada1-767463f4b8b1</t>
         </is>
       </c>
-      <c r="Q83" t="inlineStr">
+      <c r="R83" t="inlineStr">
         <is>
           <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
         </is>
@@ -4582,25 +4973,30 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O84" t="inlineStr">
+      <c r="P84" t="inlineStr">
         <is>
           <t>cfbeee97-432b-4263-a7e2-20492b6833aa</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>47df9b3a-dfe5-48f1-8c75-b3a2a221f404</t>
         </is>
       </c>
-      <c r="Q84" t="inlineStr">
+      <c r="R84" t="inlineStr">
         <is>
           <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
         </is>
@@ -4639,25 +5035,30 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O85" t="inlineStr">
+      <c r="P85" t="inlineStr">
         <is>
           <t>4a44d096-425c-4067-a05d-ef151d6deb99</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>18c62048-2b6f-46dd-8b2e-f845a8fb9287</t>
         </is>
       </c>
-      <c r="Q85" t="inlineStr">
+      <c r="R85" t="inlineStr">
         <is>
           <t>3ba28285-55f5-4b5d-8de1-aec6d11f8488</t>
         </is>
@@ -4701,20 +5102,25 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr">
+      <c r="P86" t="inlineStr">
         <is>
           <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>4ec9d487-7a5b-4f09-9b2e-c7316873bab2</t>
         </is>
@@ -4753,20 +5159,25 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr">
+      <c r="P87" t="inlineStr">
         <is>
           <t>a5cb7052-ba1f-4451-af2a-19be86f0f2d5</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>7b3fbc36-00ce-49a1-81c2-c3f4245c91a3</t>
         </is>
       </c>
-      <c r="Q87" t="inlineStr">
+      <c r="R87" t="inlineStr">
         <is>
           <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
         </is>
@@ -4805,25 +5216,30 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
           <t>L</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr">
+      <c r="P88" t="inlineStr">
         <is>
           <t>a48608e8-1cd8-4504-8093-2ba46ddcf3b5</t>
         </is>
       </c>
-      <c r="P88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>f46e6f0e-0ead-4035-927a-0da05637d7bb</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr">
+      <c r="R88" t="inlineStr">
         <is>
           <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
         </is>
@@ -4862,25 +5278,30 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="P89" t="inlineStr">
         <is>
           <t>e7b83a88-e3a4-4ac1-95df-1c49fb5c03d1</t>
         </is>
       </c>
-      <c r="P89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>2b436f91-4f96-4547-adb6-fc94cf16ef56</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr">
+      <c r="R89" t="inlineStr">
         <is>
           <t>cd2a0930-4241-4f8e-a1f2-8151b9814368</t>
         </is>
@@ -4924,20 +5345,25 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>CSc</t>
         </is>
       </c>
-      <c r="O90" t="inlineStr">
+      <c r="P90" t="inlineStr">
         <is>
           <t>40a9fa54-4a0b-4476-8309-5af5eb811950</t>
         </is>
       </c>
-      <c r="P90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>4fffe2cf-97b3-4e53-85f8-92cd71d03f6c</t>
         </is>
@@ -4981,20 +5407,25 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>MS</t>
         </is>
       </c>
-      <c r="O91" t="inlineStr">
+      <c r="P91" t="inlineStr">
         <is>
           <t>a5b44d75-f4c2-4bec-ac92-627e21532342</t>
         </is>
       </c>
-      <c r="P91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>de022131-2fc1-4891-9403-47dd5f360b91</t>
         </is>
@@ -5003,7 +5434,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>WS 4</t>
+          <t>WS+4</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5038,15 +5469,20 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
           <t>m</t>
         </is>
       </c>
-      <c r="O92" t="inlineStr">
+      <c r="P92" t="inlineStr">
         <is>
           <t>7439cc3f-ce60-45de-aa27-01f58633f31e</t>
         </is>
       </c>
-      <c r="P92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>80534827-d6e9-4aa2-a626-f974adc6d519</t>
         </is>
@@ -5055,7 +5491,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>FC,df+4,3</t>
+          <t>FC+df+4,3</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5090,15 +5526,20 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="O93" t="inlineStr">
+      <c r="P93" t="inlineStr">
         <is>
           <t>f4f51a05-dcc8-4a5f-a2e8-a423c1aceae5</t>
         </is>
       </c>
-      <c r="P93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>58440e18-0289-46f8-8663-32eb0a369a60</t>
         </is>
@@ -5107,12 +5548,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>FC 1+3</t>
+          <t>FC+1+3</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FC 2+4; d+1+3; d+2+4</t>
+          <t>FC+2+4; d+1+3; d+2+4</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5130,12 +5571,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
         <is>
           <t>378397f9-a5c6-48bc-b260-44dfff87353f</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>a345769d-6667-4346-9926-12c8e2c5fa20</t>
         </is>
@@ -5162,12 +5608,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O95" t="inlineStr">
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
         <is>
           <t>9acdca23-e347-4844-ac7f-41cf9fb1455f</t>
         </is>
       </c>
-      <c r="P95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t>83bfe4a8-8088-46fd-9d6a-08e13311a449</t>
         </is>
@@ -5199,12 +5650,12 @@
       </c>
       <c r="D98" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E98" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F98" s="1" t="inlineStr">
@@ -5229,45 +5680,50 @@
       </c>
       <c r="J98" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K98" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K98" s="1" t="inlineStr">
+      <c r="L98" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L98" s="1" t="inlineStr">
+      <c r="M98" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M98" s="1" t="inlineStr">
+      <c r="N98" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N98" s="1" t="inlineStr">
+      <c r="O98" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O98" s="1" t="inlineStr">
+      <c r="P98" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P98" s="1" t="inlineStr">
+      <c r="Q98" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q98" s="1" t="inlineStr">
+      <c r="R98" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R98" s="1" t="inlineStr">
+      <c r="S98" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -5306,20 +5762,25 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
           <t>!</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="O99" t="inlineStr">
+      <c r="P99" t="inlineStr">
         <is>
           <t>24a1499c-dbb1-4e04-b918-cb20db832fa6</t>
         </is>
       </c>
-      <c r="P99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>b4ced4c1-763a-4eb4-b61f-c12c50bd284b</t>
         </is>
@@ -5351,12 +5812,12 @@
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
-          <t>Stance</t>
+          <t>To Stance</t>
         </is>
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t>Hit</t>
+          <t>Speed</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
@@ -5381,45 +5842,50 @@
       </c>
       <c r="J102" s="1" t="inlineStr">
         <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K102" s="1" t="inlineStr">
+        <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="K102" s="1" t="inlineStr">
+      <c r="L102" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="L102" s="1" t="inlineStr">
+      <c r="M102" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="M102" s="1" t="inlineStr">
+      <c r="N102" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="N102" s="1" t="inlineStr">
+      <c r="O102" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="O102" s="1" t="inlineStr">
+      <c r="P102" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="P102" s="1" t="inlineStr">
+      <c r="Q102" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="Q102" s="1" t="inlineStr">
+      <c r="R102" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="R102" s="1" t="inlineStr">
+      <c r="S102" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -5438,15 +5904,20 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
           <t>hmmhLmhhLm</t>
         </is>
       </c>
-      <c r="P103" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>f26af970-57e3-45d4-baba-6711c2809508</t>
         </is>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -5465,15 +5936,20 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
           <t>hmmhLmmLm!</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
         </is>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="S104" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -5492,15 +5968,20 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
           <t>hmmhLmmmLm</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>12d35c24-0209-43bc-a4fa-a6173fd493c0</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="S105" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/julia_step5.xlsx
+++ b/sources/julia_step5.xlsx
@@ -863,6 +863,11 @@
           <t>Special Tag Throw with Michelle only. Michelle finishes with a Lariat. Total damage is 12,24.</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
+        </is>
+      </c>
       <c r="Q9" t="inlineStr">
         <is>
           <t>1b569aeb-dd63-4db9-bfe2-caa3a868a11d</t>
@@ -910,6 +915,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
+        </is>
+      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>48718773-f00b-471d-8dc4-830794a42ebc</t>
@@ -957,6 +967,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
+        </is>
+      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>35dc67c0-d4fa-495c-aefc-39f34e65507b</t>
@@ -1002,6 +1017,11 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>b70b8f8a-633b-40a2-8811-5f4191813631</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -5912,6 +5932,11 @@
           <t>hmmhLmhhLm</t>
         </is>
       </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>f26af970-57e3-45d4-baba-6711c2809508</t>
+        </is>
+      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>f26af970-57e3-45d4-baba-6711c2809508</t>
@@ -5944,6 +5969,11 @@
           <t>hmmhLmmLm!</t>
         </is>
       </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
+        </is>
+      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>8ba99c8f-7b6d-46d5-860f-492405778df4</t>
@@ -5974,6 +6004,11 @@
       <c r="K105" t="inlineStr">
         <is>
           <t>hmmhLmmmLm</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>12d35c24-0209-43bc-a4fa-a6173fd493c0</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">

--- a/sources/julia_step5.xlsx
+++ b/sources/julia_step5.xlsx
@@ -4133,6 +4133,11 @@
           <t>– 1+2</t>
         </is>
       </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>– Back Push</t>
